--- a/out/MLP-Mamba1_repeat_1_000007.xlsx
+++ b/out/MLP-Mamba1_repeat_1_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.544994382064366</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.544994382064366</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.544994382064366</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.5730533708028094</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.5730533708028094</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.944994382064366</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.5730533708028094</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.544994382064366</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.544994382064366</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.544994382064366</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.544994382064366</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.000294076475623995</v>
+        <v>-0.000247312392486725</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.390267440835934</v>
+        <v>2.851146552728524</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.5730533708028094</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC40" t="n">
-        <v>6.785775623298086</v>
+        <v>5.70670061504017</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.5083857259756837</v>
+        <v>0.4275421665970212</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.544994382064366</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.407729429176656</v>
+        <v>3.706811613138676</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.6356475187464935</v>
+        <v>0.5345667647300912</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.544994382064366</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC42" t="n">
-        <v>5.170719589469075</v>
+        <v>4.348470986255929</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.9111978663021727</v>
+        <v>0.7662990847851953</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.544994382064366</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC43" t="n">
-        <v>6.357826413938764</v>
+        <v>5.346803957364659</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.9748008790059393</v>
+        <v>0.8197882323621565</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.544994382064366</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC44" t="n">
-        <v>7.396298939575981</v>
+        <v>6.220138471186094</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.033093189275808</v>
+        <v>0.8688102903327571</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.544994382064366</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC45" t="n">
-        <v>8.487757506227002</v>
+        <v>7.138032852856522</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4662157420527285</v>
+        <v>0.3920772593576683</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.544994382064366</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC46" t="n">
-        <v>8.38623730472084</v>
+        <v>7.052656436075132</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2251608943023893</v>
+        <v>0.1893560389367799</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC47" t="n">
-        <v>8.369977774425758</v>
+        <v>7.03898247967525</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1072824626685446</v>
+        <v>0.0902219021696837</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC48" t="n">
-        <v>8.359202996494439</v>
+        <v>7.029921096852586</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.03178668214998914</v>
+        <v>0.02673248346626829</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.944994382064366</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC49" t="n">
-        <v>8.315380348975356</v>
+        <v>6.99306683114631</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02102570490037912</v>
+        <v>0.01768254094478411</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.944994382064366</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC50" t="n">
-        <v>8.325628714414307</v>
+        <v>7.001685471441498</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01075946898473934</v>
+        <v>0.009047387080402371</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC51" t="n">
-        <v>8.32610805826077</v>
+        <v>7.002087784324966</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.005501441891907545</v>
+        <v>0.004625645832317131</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC52" t="n">
-        <v>8.3263450923232</v>
+        <v>7.002286326640508</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.002065080248495467</v>
+        <v>0.001735835309520868</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.944994382064366</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC53" t="n">
-        <v>8.324969389133802</v>
+        <v>7.001128593141697</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001123608176889768</v>
+        <v>0.0009437568738473929</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC54" t="n">
-        <v>8.325149614748652</v>
+        <v>7.001279370012054</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0005385952861818967</v>
+        <v>0.0004519697215710388</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.544994382064366</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC55" t="n">
-        <v>8.325102483499061</v>
+        <v>7.001238922348024</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003315126501627838</v>
+        <v>0.0002783790738212916</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.544994382064366</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC56" t="n">
-        <v>8.325226659322402</v>
+        <v>7.001342701988732</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001710221259300122</v>
+        <v>0.0001432291586779051</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.5730533708028094</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC57" t="n">
-        <v>8.325236995407543</v>
+        <v>7.001350616586747</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.99229161167401e-05</v>
+        <v>6.69347054165328e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.544994382064366</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC58" t="n">
-        <v>8.325226708616551</v>
+        <v>7.001341164040176</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.00032942437966e-05</v>
+        <v>4.104926959945762e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.544994382064366</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC59" t="n">
-        <v>8.32524575537068</v>
+        <v>7.001356296206423</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.947783683037037e-05</v>
+        <v>1.598100299746031e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5730533708028094</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC60" t="n">
-        <v>8.325235837756075</v>
+        <v>7.001347178540911</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>6.323060732339969e-06</v>
+        <v>4.264322417369065e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.544994382064366</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC61" t="n">
-        <v>8.325227823050861</v>
+        <v>7.001339711963916</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>5.63141154556023e-07</v>
+        <v>-5.494870763551826e-07</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC62" t="n">
-        <v>8.325223733238371</v>
+        <v>7.001335456785746</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC63" t="n">
-        <v>8.325217865795686</v>
+        <v>7.001329734506715</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.944994382064366</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC64" t="n">
-        <v>8.325212796440319</v>
+        <v>7.001324665151347</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.544994382064366</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC65" t="n">
-        <v>8.325208431466351</v>
+        <v>7.001320300177378</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.544994382064366</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC66" t="n">
-        <v>8.325209522712806</v>
+        <v>7.001321391423835</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.5730533708028094</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC67" t="n">
-        <v>8.32520883310567</v>
+        <v>7.001320701816699</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC68" t="n">
-        <v>8.325208863418073</v>
+        <v>7.001320732129101</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC69" t="n">
-        <v>8.325208673965562</v>
+        <v>7.001320542676591</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC70" t="n">
-        <v>8.325208727012265</v>
+        <v>7.001320595723294</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC71" t="n">
-        <v>8.325208780058967</v>
+        <v>7.001320648769996</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC72" t="n">
-        <v>8.325208742168465</v>
+        <v>7.001320610879494</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC73" t="n">
-        <v>8.325208613340759</v>
+        <v>7.001320482051787</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC74" t="n">
-        <v>8.325208469356852</v>
+        <v>7.00132033806788</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC75" t="n">
-        <v>8.325208310216743</v>
+        <v>7.001320178927772</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC76" t="n">
-        <v>8.325208363263448</v>
+        <v>7.001320231974474</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC77" t="n">
-        <v>8.325208310216743</v>
+        <v>7.001320178927772</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC78" t="n">
-        <v>8.325208310216743</v>
+        <v>7.001320178927772</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>2.544994382064366</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC79" t="n">
-        <v>8.325208128342334</v>
+        <v>7.001319997053362</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.544994382064366</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC80" t="n">
-        <v>8.325208295060543</v>
+        <v>7.00132016377157</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5730533708028094</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC81" t="n">
-        <v>8.325208492091154</v>
+        <v>7.001320360802181</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5730533708028094</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC82" t="n">
-        <v>8.325208332951044</v>
+        <v>7.001320201662073</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.544994382064366</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC83" t="n">
-        <v>8.325208370841546</v>
+        <v>7.001320239552574</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.544994382064366</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC84" t="n">
-        <v>8.325208567872158</v>
+        <v>7.001320436583184</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5730533708028094</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC85" t="n">
-        <v>8.325208545137857</v>
+        <v>7.001320413848884</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC86" t="n">
-        <v>8.325208393575847</v>
+        <v>7.001320262286876</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC87" t="n">
-        <v>8.325208317794845</v>
+        <v>7.001320186505872</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC88" t="n">
-        <v>8.325208416310149</v>
+        <v>7.001320285021177</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.944994382064366</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC89" t="n">
-        <v>8.325208423888249</v>
+        <v>7.001320292599278</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5730533708028094</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC90" t="n">
-        <v>8.325208689121762</v>
+        <v>7.001320557832791</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.544994382064366</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC91" t="n">
-        <v>8.325208393575847</v>
+        <v>7.001320262286876</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.544994382064366</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC92" t="n">
-        <v>8.325208636075061</v>
+        <v>7.001320504786088</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5730533708028094</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC93" t="n">
-        <v>8.325208719434164</v>
+        <v>7.001320588145193</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.544994382064366</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC94" t="n">
-        <v>8.325208552715955</v>
+        <v>7.001320421426985</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC95" t="n">
-        <v>8.325208742168465</v>
+        <v>7.001320610879494</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC96" t="n">
-        <v>8.325208393575847</v>
+        <v>7.001320262286876</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC97" t="n">
-        <v>8.325208188967137</v>
+        <v>7.001320057678165</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC98" t="n">
-        <v>8.325208302638643</v>
+        <v>7.001320171349671</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC99" t="n">
-        <v>8.325208317794845</v>
+        <v>7.001320186505872</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC100" t="n">
-        <v>8.325208082873733</v>
+        <v>7.00131995158476</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC101" t="n">
-        <v>8.325208143498534</v>
+        <v>7.001320012209563</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC102" t="n">
-        <v>8.325208014670828</v>
+        <v>7.001319883381855</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.544994382064366</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC103" t="n">
-        <v>8.325208151076636</v>
+        <v>7.001320019787664</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5730533708028094</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC104" t="n">
-        <v>8.325208325372945</v>
+        <v>7.001320194083972</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5730533708028094</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC105" t="n">
-        <v>8.325208469356852</v>
+        <v>7.00132033806788</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC106" t="n">
-        <v>8.325208302638643</v>
+        <v>7.001320171349671</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC107" t="n">
-        <v>8.325208295060543</v>
+        <v>7.00132016377157</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC108" t="n">
-        <v>8.325208007092728</v>
+        <v>7.001319875803755</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC109" t="n">
-        <v>8.325208022248928</v>
+        <v>7.001319890959957</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC110" t="n">
-        <v>8.325208249591942</v>
+        <v>7.001320118302968</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>2.544994382064366</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC111" t="n">
-        <v>8.325208234435738</v>
+        <v>7.001320103146767</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5730533708028094</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC112" t="n">
-        <v>8.325208340529146</v>
+        <v>7.001320209240173</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5730533708028094</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC113" t="n">
-        <v>8.325208067717529</v>
+        <v>7.001319936428559</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC114" t="n">
-        <v>8.325208166232835</v>
+        <v>7.001320034943864</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC115" t="n">
-        <v>8.325208317794845</v>
+        <v>7.001320186505872</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC116" t="n">
-        <v>8.325208332951044</v>
+        <v>7.001320201662073</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC117" t="n">
-        <v>8.325208310216743</v>
+        <v>7.001320178927772</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC118" t="n">
-        <v>8.325208393575847</v>
+        <v>7.001320262286876</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC119" t="n">
-        <v>8.325208492091154</v>
+        <v>7.001320360802181</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC120" t="n">
-        <v>8.325208325372945</v>
+        <v>7.001320194083972</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC121" t="n">
-        <v>8.325208310216743</v>
+        <v>7.001320178927772</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC122" t="n">
-        <v>8.325208279904341</v>
+        <v>7.00132014861537</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC123" t="n">
-        <v>8.325208264748142</v>
+        <v>7.00132013345917</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC124" t="n">
-        <v>8.325208302638643</v>
+        <v>7.001320171349671</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC125" t="n">
-        <v>8.325208317794845</v>
+        <v>7.001320186505872</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC126" t="n">
-        <v>8.325208310216743</v>
+        <v>7.001320178927772</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_1_000007.xlsx
+++ b/out/MLP-Mamba1_repeat_1_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.2740314606762853</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.544994382064366</v>
+        <v>0.9867280899030685</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129851</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.544994382064366</v>
+        <v>0.9867280899030685</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.5730533708028094</v>
+        <v>0.2740314606762853</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.5730533708028094</v>
+        <v>-0.4386651685504979</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.07403146067628527</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.944994382064366</v>
+        <v>0.07403146067628522</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.07403146067628522</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.5730533708028094</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.07403146067628527</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.544994382064366</v>
+        <v>0.9867280899030685</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129851</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129851</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.544994382064366</v>
+        <v>0.9867280899030685</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.000294076475623995</v>
+        <v>-0.0001752460243899841</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.390267440835934</v>
+        <v>2.020327763775675</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.5730533708028094</v>
+        <v>0.9867280899030685</v>
       </c>
       <c r="JC40" t="n">
-        <v>6.785775623298086</v>
+        <v>4.043778741223575</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.5083857259756837</v>
+        <v>0.3029571830973454</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.544994382064366</v>
+        <v>0.9867280899030685</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.407729429176656</v>
+        <v>2.626653634369472</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.6356475187464935</v>
+        <v>0.378795054764096</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129851</v>
       </c>
       <c r="JC42" t="n">
-        <v>5.170719589469075</v>
+        <v>3.081334672513782</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.9111978663021727</v>
+        <v>0.5430007519311153</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129851</v>
       </c>
       <c r="JC43" t="n">
-        <v>6.357826413938764</v>
+        <v>3.788755218031177</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.9748008790059393</v>
+        <v>0.5809035951539512</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129851</v>
       </c>
       <c r="JC44" t="n">
-        <v>7.396298939575981</v>
+        <v>4.407601816242384</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.033093189275808</v>
+        <v>0.6156407243207273</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129851</v>
       </c>
       <c r="JC45" t="n">
-        <v>8.487757506227002</v>
+        <v>5.05802362669893</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4662157420527285</v>
+        <v>0.2778272087228331</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.544994382064366</v>
+        <v>0.9867280899030685</v>
       </c>
       <c r="JC46" t="n">
-        <v>8.38623730472084</v>
+        <v>4.997525724827898</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2251608943023893</v>
+        <v>0.1341778432923329</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.07403146067628533</v>
       </c>
       <c r="JC47" t="n">
-        <v>8.369977774425758</v>
+        <v>4.987836348194802</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1072824626685446</v>
+        <v>0.06393113470456169</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.07403146067628533</v>
       </c>
       <c r="JC48" t="n">
-        <v>8.359202996494439</v>
+        <v>4.9814154452235</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.03178668214998914</v>
+        <v>0.01894271245675084</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.944994382064366</v>
+        <v>0.7867280899030684</v>
       </c>
       <c r="JC49" t="n">
-        <v>8.315380348975356</v>
+        <v>4.955300409598037</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02102570490037912</v>
+        <v>0.01252871394212684</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.944994382064366</v>
+        <v>0.7867280899030684</v>
       </c>
       <c r="JC50" t="n">
-        <v>8.325628714414307</v>
+        <v>4.961406418221427</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01075946898473934</v>
+        <v>0.006409403410559028</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.07403146067628533</v>
       </c>
       <c r="JC51" t="n">
-        <v>8.32610805826077</v>
+        <v>4.961690041442948</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.005501441891907545</v>
+        <v>0.003276718568120401</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.07403146067628533</v>
       </c>
       <c r="JC52" t="n">
-        <v>8.3263450923232</v>
+        <v>4.961829274885305</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.002065080248495467</v>
+        <v>0.001228722415008268</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.944994382064366</v>
+        <v>0.07403146067628533</v>
       </c>
       <c r="JC53" t="n">
-        <v>8.324969389133802</v>
+        <v>4.961007514895289</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001123608176889768</v>
+        <v>0.0006673798714657611</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.7867280899030684</v>
       </c>
       <c r="JC54" t="n">
-        <v>8.325149614748652</v>
+        <v>4.961112864950918</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0005385952861818967</v>
+        <v>0.0003184550898772397</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.544994382064366</v>
+        <v>0.9867280899030685</v>
       </c>
       <c r="JC55" t="n">
-        <v>8.325102483499061</v>
+        <v>4.961082765313102</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003315126501627838</v>
+        <v>0.0001957268439567483</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.544994382064366</v>
+        <v>0.9867280899030685</v>
       </c>
       <c r="JC56" t="n">
-        <v>8.325226659322402</v>
+        <v>4.961154817558604</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001710221259300122</v>
+        <v>9.999565406351607e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.5730533708028094</v>
+        <v>0.9867280899030685</v>
       </c>
       <c r="JC57" t="n">
-        <v>8.325236995407543</v>
+        <v>4.961158965398864</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.99229161167401e-05</v>
+        <v>4.595374967004406e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.544994382064366</v>
+        <v>0.9867280899030685</v>
       </c>
       <c r="JC58" t="n">
-        <v>8.325226708616551</v>
+        <v>4.961150811511709</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.00032942437966e-05</v>
+        <v>2.697865944406779e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.544994382064366</v>
+        <v>0.9867280899030685</v>
       </c>
       <c r="JC59" t="n">
-        <v>8.32524575537068</v>
+        <v>4.961160072572429</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.947783683037037e-05</v>
+        <v>1.015294660927689e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5730533708028094</v>
+        <v>0.9867280899030685</v>
       </c>
       <c r="JC60" t="n">
-        <v>8.325235837756075</v>
+        <v>4.961152098702891</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>6.323060732339969e-06</v>
+        <v>1.176214944912711e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.544994382064366</v>
+        <v>0.07403146067628529</v>
       </c>
       <c r="JC61" t="n">
-        <v>8.325227823050861</v>
+        <v>4.961145317912421</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>5.63141154556023e-07</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.07403146067628529</v>
       </c>
       <c r="JC62" t="n">
-        <v>8.325223733238371</v>
+        <v>4.961140897368571</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.07403146067628527</v>
       </c>
       <c r="JC63" t="n">
-        <v>8.325217865795686</v>
+        <v>4.961135319073447</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.944994382064366</v>
+        <v>0.7867280899030684</v>
       </c>
       <c r="JC64" t="n">
-        <v>8.325212796440319</v>
+        <v>4.96113027245238</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129851</v>
       </c>
       <c r="JC65" t="n">
-        <v>8.325208431466351</v>
+        <v>4.961130590732596</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.544994382064366</v>
+        <v>0.9867280899030685</v>
       </c>
       <c r="JC66" t="n">
-        <v>8.325209522712806</v>
+        <v>4.961131681979053</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.5730533708028094</v>
+        <v>0.2740314606762854</v>
       </c>
       <c r="JC67" t="n">
-        <v>8.32520883310567</v>
+        <v>4.961130992371917</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC68" t="n">
-        <v>8.325208863418073</v>
+        <v>4.961131022684319</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC69" t="n">
-        <v>8.325208673965562</v>
+        <v>4.961130833231809</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC70" t="n">
-        <v>8.325208727012265</v>
+        <v>4.961130886278512</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC71" t="n">
-        <v>8.325208780058967</v>
+        <v>4.961130939325215</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC72" t="n">
-        <v>8.325208742168465</v>
+        <v>4.961130901434712</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC73" t="n">
-        <v>8.325208613340759</v>
+        <v>4.961130772607005</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC74" t="n">
-        <v>8.325208469356852</v>
+        <v>4.961130628623098</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC75" t="n">
-        <v>8.325208310216743</v>
+        <v>4.96113046948299</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC76" t="n">
-        <v>8.325208363263448</v>
+        <v>4.961130522529692</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC77" t="n">
-        <v>8.325208310216743</v>
+        <v>4.96113046948299</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.2740314606762854</v>
       </c>
       <c r="JC78" t="n">
-        <v>8.325208310216743</v>
+        <v>4.96113046948299</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>2.544994382064366</v>
+        <v>0.9867280899030685</v>
       </c>
       <c r="JC79" t="n">
-        <v>8.325208128342334</v>
+        <v>4.96113028760858</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.544994382064366</v>
+        <v>0.9867280899030685</v>
       </c>
       <c r="JC80" t="n">
-        <v>8.325208295060543</v>
+        <v>4.961130454326788</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5730533708028094</v>
+        <v>0.2740314606762854</v>
       </c>
       <c r="JC81" t="n">
-        <v>8.325208492091154</v>
+        <v>4.961130651357399</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5730533708028094</v>
+        <v>0.2740314606762854</v>
       </c>
       <c r="JC82" t="n">
-        <v>8.325208332951044</v>
+        <v>4.961130492217291</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.544994382064366</v>
+        <v>0.9867280899030685</v>
       </c>
       <c r="JC83" t="n">
-        <v>8.325208370841546</v>
+        <v>4.961130530107792</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.544994382064366</v>
+        <v>0.9867280899030685</v>
       </c>
       <c r="JC84" t="n">
-        <v>8.325208567872158</v>
+        <v>4.961130727138403</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5730533708028094</v>
+        <v>0.2740314606762854</v>
       </c>
       <c r="JC85" t="n">
-        <v>8.325208545137857</v>
+        <v>4.961130704404102</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC86" t="n">
-        <v>8.325208393575847</v>
+        <v>4.961130552842094</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC87" t="n">
-        <v>8.325208317794845</v>
+        <v>4.96113047706109</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.07403146067628533</v>
       </c>
       <c r="JC88" t="n">
-        <v>8.325208416310149</v>
+        <v>4.961130575576396</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.944994382064366</v>
+        <v>0.07403146067628533</v>
       </c>
       <c r="JC89" t="n">
-        <v>8.325208423888249</v>
+        <v>4.961130583154496</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5730533708028094</v>
+        <v>0.9867280899030685</v>
       </c>
       <c r="JC90" t="n">
-        <v>8.325208689121762</v>
+        <v>4.961130848388009</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.544994382064366</v>
+        <v>0.9867280899030685</v>
       </c>
       <c r="JC91" t="n">
-        <v>8.325208393575847</v>
+        <v>4.961130552842094</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.544994382064366</v>
+        <v>0.9867280899030685</v>
       </c>
       <c r="JC92" t="n">
-        <v>8.325208636075061</v>
+        <v>4.961130795341306</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5730533708028094</v>
+        <v>0.9867280899030685</v>
       </c>
       <c r="JC93" t="n">
-        <v>8.325208719434164</v>
+        <v>4.961130878700411</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.544994382064366</v>
+        <v>0.2740314606762853</v>
       </c>
       <c r="JC94" t="n">
-        <v>8.325208552715955</v>
+        <v>4.961130711982203</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.2740314606762853</v>
       </c>
       <c r="JC95" t="n">
-        <v>8.325208742168465</v>
+        <v>4.961130901434712</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC96" t="n">
-        <v>8.325208393575847</v>
+        <v>4.961130552842094</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC97" t="n">
-        <v>8.325208188967137</v>
+        <v>4.961130348233383</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC98" t="n">
-        <v>8.325208302638643</v>
+        <v>4.961130461904889</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC99" t="n">
-        <v>8.325208317794845</v>
+        <v>4.96113047706109</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC100" t="n">
-        <v>8.325208082873733</v>
+        <v>4.961130242139978</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC101" t="n">
-        <v>8.325208143498534</v>
+        <v>4.961130302764781</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.07403146067628527</v>
       </c>
       <c r="JC102" t="n">
-        <v>8.325208014670828</v>
+        <v>4.961130173937074</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.544994382064366</v>
+        <v>0.2740314606762853</v>
       </c>
       <c r="JC103" t="n">
-        <v>8.325208151076636</v>
+        <v>4.961130310342882</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5730533708028094</v>
+        <v>0.2740314606762853</v>
       </c>
       <c r="JC104" t="n">
-        <v>8.325208325372945</v>
+        <v>4.96113048463919</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5730533708028094</v>
+        <v>-0.4386651685504979</v>
       </c>
       <c r="JC105" t="n">
-        <v>8.325208469356852</v>
+        <v>4.961130628623098</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4386651685504979</v>
       </c>
       <c r="JC106" t="n">
-        <v>8.325208302638643</v>
+        <v>4.961130461904889</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC107" t="n">
-        <v>8.325208295060543</v>
+        <v>4.961130454326788</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC108" t="n">
-        <v>8.325208007092728</v>
+        <v>4.961130166358974</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC109" t="n">
-        <v>8.325208022248928</v>
+        <v>4.961130181515175</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.07403146067628527</v>
       </c>
       <c r="JC110" t="n">
-        <v>8.325208249591942</v>
+        <v>4.961130408858186</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>2.544994382064366</v>
+        <v>0.2740314606762853</v>
       </c>
       <c r="JC111" t="n">
-        <v>8.325208234435738</v>
+        <v>4.961130393701985</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5730533708028094</v>
+        <v>0.2740314606762853</v>
       </c>
       <c r="JC112" t="n">
-        <v>8.325208340529146</v>
+        <v>4.961130499795392</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5730533708028094</v>
+        <v>-0.4386651685504979</v>
       </c>
       <c r="JC113" t="n">
-        <v>8.325208067717529</v>
+        <v>4.961130226983777</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4386651685504979</v>
       </c>
       <c r="JC114" t="n">
-        <v>8.325208166232835</v>
+        <v>4.961130325499082</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC115" t="n">
-        <v>8.325208317794845</v>
+        <v>4.96113047706109</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC116" t="n">
-        <v>8.325208332951044</v>
+        <v>4.961130492217291</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC117" t="n">
-        <v>8.325208310216743</v>
+        <v>4.96113046948299</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC118" t="n">
-        <v>8.325208393575847</v>
+        <v>4.961130552842094</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC119" t="n">
-        <v>8.325208492091154</v>
+        <v>4.961130651357399</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC120" t="n">
-        <v>8.325208325372945</v>
+        <v>4.96113048463919</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC121" t="n">
-        <v>8.325208310216743</v>
+        <v>4.96113046948299</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC122" t="n">
-        <v>8.325208279904341</v>
+        <v>4.961130439170588</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC123" t="n">
-        <v>8.325208264748142</v>
+        <v>4.961130424014388</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC124" t="n">
-        <v>8.325208302638643</v>
+        <v>4.961130461904889</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC125" t="n">
-        <v>8.325208317794845</v>
+        <v>4.96113047706109</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC126" t="n">
-        <v>8.325208310216743</v>
+        <v>4.96113046948299</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_1_000007.xlsx
+++ b/out/MLP-Mamba1_repeat_1_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4272740483283997</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-1.14</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4449216425418854</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9299999999999997</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.4269764423370361</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.4639944732189178</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4723112285137177</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.435956597328186</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.4131077527999878</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4074170589447021</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4412376582622528</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4204380214214325</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4183961749076843</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.4096227288246155</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.456941545009613</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4012509286403656</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.4209989011287689</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.4207866787910461</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4534048438072205</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4110492765903473</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4446877837181091</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.2740314606762853</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.5027844905853271</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.9867280899030685</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.5233585238456726</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.699424719129851</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.5655902028083801</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.9867280899030685</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.439707338809967</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.2740314606762853</v>
+        <v>0.16</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.436781644821167</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.4386651685504979</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.425338089466095</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.407292902469635</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.3936907649040222</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.07403146067628527</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.504987895488739</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.07403146067628522</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4182033836841583</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.07403146067628522</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4248292148113251</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4073186218738556</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.3671960830688477</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4311227202415466</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.4391472339630127</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.07403146067628527</v>
+        <v>0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.5501731038093567</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.9867280899030685</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.6767249703407288</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.699424719129851</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.5303729176521301</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.699424719129851</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.5654799342155457</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.9867280899030685</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001752460243899841</v>
+        <v>-0.0001655819800505415</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.020327763775675</v>
+        <v>1.908915605419707</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.465579479932785</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.9867280899030685</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>4.043778741223575</v>
+        <v>3.820782201421234</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.3029571830973454</v>
+        <v>0.2862504102768729</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.5198519825935364</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.9867280899030685</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
-        <v>2.626653634369472</v>
+        <v>2.481805283148065</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.378795054764096</v>
+        <v>0.3579062094468367</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.509793758392334</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.699424719129851</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC42" t="n">
-        <v>3.081334672513782</v>
+        <v>2.911412704952789</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.5430007519311153</v>
+        <v>0.5130568539070393</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.6155952215194702</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.699424719129851</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>3.788755218031177</v>
+        <v>3.579822185635244</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.5809035951539512</v>
+        <v>0.5488688594293036</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.682673454284668</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.699424719129851</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>4.407601816242384</v>
+        <v>4.164541999836108</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.6156407243207273</v>
+        <v>0.5816910990992846</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.6774502992630005</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.699424719129851</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>5.05802362669893</v>
+        <v>4.779096175439199</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.2778272087228331</v>
+        <v>0.2625057084191442</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.6064868569374084</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.9867280899030685</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC46" t="n">
-        <v>4.997525724827898</v>
+        <v>4.721934442921425</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1341778432923329</v>
+        <v>0.1267789021009197</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>0.4933322072029114</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.07403146067628533</v>
+        <v>-0.16</v>
       </c>
       <c r="JC47" t="n">
-        <v>4.987836348194802</v>
+        <v>4.712779365589396</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.06393113470456169</v>
+        <v>0.06040575950735491</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.3766611218452454</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.07403146067628533</v>
+        <v>-0.3</v>
       </c>
       <c r="JC48" t="n">
-        <v>4.9814154452235</v>
+        <v>4.706712529200177</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01894271245675084</v>
+        <v>0.01789816837695915</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.5336716771125793</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.7867280899030684</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>4.955300409598037</v>
+        <v>4.682037535803007</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01252871394212684</v>
+        <v>0.01183757656008916</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.5310116410255432</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.7867280899030684</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>4.961406418221427</v>
+        <v>4.687806569566344</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.006409403410559028</v>
+        <v>0.006056163523399848</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.4134324193000793</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.07403146067628533</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>4.961690041442948</v>
+        <v>4.688074276883612</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.003276718568120401</v>
+        <v>0.003095519383377557</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.4739493131637573</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.07403146067628533</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>4.961829274885305</v>
+        <v>4.68820554651627</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001228722415008268</v>
+        <v>0.001160602772461799</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.5013241171836853</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.07403146067628533</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>4.961007514895289</v>
+        <v>4.687428883703615</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0006673798714657611</v>
+        <v>0.0006302546024891238</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.4890816509723663</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.7867280899030684</v>
+        <v>-0.3</v>
       </c>
       <c r="JC54" t="n">
-        <v>4.961112864950918</v>
+        <v>4.687528140811389</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0003184550898772397</v>
+        <v>0.0003009710309649564</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.5259160995483398</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.9867280899030685</v>
+        <v>0.3</v>
       </c>
       <c r="JC55" t="n">
-        <v>4.961082765313102</v>
+        <v>4.687499426584645</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0001957268439567483</v>
+        <v>0.0001839193825475277</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.5189248323440552</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.9867280899030685</v>
+        <v>0.3</v>
       </c>
       <c r="JC56" t="n">
-        <v>4.961154817558604</v>
+        <v>4.687567135797627</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>9.999565406351607e-05</v>
+        <v>9.381943911860337e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.3869617581367493</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.9867280899030685</v>
+        <v>0.3</v>
       </c>
       <c r="JC57" t="n">
-        <v>4.961158965398864</v>
+        <v>4.68757079099824</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>4.595374967004406e-05</v>
+        <v>4.295647027768853e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.7570429444313049</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.9867280899030685</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>4.961150811511709</v>
+        <v>4.687562792321457</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.697865944406779e-05</v>
+        <v>2.569951306630508e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.5048877000808716</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.9867280899030685</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>4.961160072572429</v>
+        <v>4.687571494155336</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.015294660927689e-05</v>
+        <v>8.987335331640211e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.450870007276535</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.9867280899030685</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>4.961152098702891</v>
+        <v>4.687563635373489</v>
       </c>
     </row>
     <row r="61">
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.5028191208839417</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.07403146067628529</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>4.961145317912421</v>
+        <v>4.687556854583018</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.4318221509456635</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.07403146067628529</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>4.961140897368571</v>
+        <v>4.687552434039168</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.466746598482132</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.07403146067628527</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>4.961135319073447</v>
+        <v>4.687546855744045</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.6227169036865234</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.7867280899030684</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>4.96113027245238</v>
+        <v>4.687541809122977</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.7622607350349426</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.699424719129851</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>4.961130590732596</v>
+        <v>4.687542127403193</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.781898558139801</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9867280899030685</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>4.961131681979053</v>
+        <v>4.68754321864965</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>0.3563120067119598</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.2740314606762854</v>
+        <v>0.16</v>
       </c>
       <c r="JC67" t="n">
-        <v>4.961130992371917</v>
+        <v>4.687542529042514</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.3449349999427795</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>4.961131022684319</v>
+        <v>4.687542559354916</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.4670529961585999</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>4.961130833231809</v>
+        <v>4.687542369902406</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.4762176275253296</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>4.961130886278512</v>
+        <v>4.687542422949109</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.405793696641922</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>4.961130939325215</v>
+        <v>4.687542475995811</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.4088332653045654</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>4.961130901434712</v>
+        <v>4.687542438105309</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.412027895450592</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>4.961130772607005</v>
+        <v>4.687542309277602</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.4292214512825012</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>4.961130628623098</v>
+        <v>4.687542165293696</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.4665920734405518</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>4.96113046948299</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.4566904902458191</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>4.961130522529692</v>
+        <v>4.68754205920029</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.4100356698036194</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>4.96113046948299</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.3853258192539215</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.2740314606762854</v>
+        <v>0.16</v>
       </c>
       <c r="JC78" t="n">
-        <v>4.96113046948299</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.5712380409240723</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.9867280899030685</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC79" t="n">
-        <v>4.96113028760858</v>
+        <v>4.687541824279178</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.5765326023101807</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.9867280899030685</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>4.961130454326788</v>
+        <v>4.687541990997386</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.3891417682170868</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.2740314606762854</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>4.961130651357399</v>
+        <v>4.687542188027996</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.4298405349254608</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.2740314606762854</v>
+        <v>0.3</v>
       </c>
       <c r="JC82" t="n">
-        <v>4.961130492217291</v>
+        <v>4.687542028887888</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.556955099105835</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.9867280899030685</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC83" t="n">
-        <v>4.961130530107792</v>
+        <v>4.68754206677839</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.5321823954582214</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.9867280899030685</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC84" t="n">
-        <v>4.961130727138403</v>
+        <v>4.687542263809</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.4376680254936218</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.2740314606762854</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>4.961130704404102</v>
+        <v>4.687542241074699</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.4286625981330872</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>4.961130552842094</v>
+        <v>4.687542089512691</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.4735119938850403</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>4.96113047706109</v>
+        <v>4.687542013731687</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>0.4702053368091583</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.07403146067628533</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>4.961130575576396</v>
+        <v>4.687542112246993</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.5715712904930115</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.07403146067628533</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>4.961130583154496</v>
+        <v>4.687542119825094</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.4783316850662231</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.9867280899030685</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>4.961130848388009</v>
+        <v>4.687542385058607</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.5300479531288147</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.9867280899030685</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>4.961130552842094</v>
+        <v>4.687542089512691</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.5713008046150208</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.9867280899030685</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>4.961130795341306</v>
+        <v>4.687542332011904</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.3821110725402832</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.9867280899030685</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>4.961130878700411</v>
+        <v>4.687542415371008</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.6560038328170776</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.2740314606762853</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC94" t="n">
-        <v>4.961130711982203</v>
+        <v>4.6875422486528</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.4161878526210785</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.2740314606762853</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>4.961130901434712</v>
+        <v>4.687542438105309</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.4573110342025757</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>4.961130552842094</v>
+        <v>4.687542089512691</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.4102557599544525</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>4.961130348233383</v>
+        <v>4.687541884903981</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.4216575026512146</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>4.961130461904889</v>
+        <v>4.687541998575486</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.3764006793498993</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>4.96113047706109</v>
+        <v>4.687542013731687</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.459093451499939</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>4.961130242139978</v>
+        <v>4.687541778810576</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.3401705920696259</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>4.961130302764781</v>
+        <v>4.687541839435378</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.4259529411792755</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.07403146067628527</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>4.961130173937074</v>
+        <v>4.687541710607671</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.6284704208374023</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.2740314606762853</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC103" t="n">
-        <v>4.961130310342882</v>
+        <v>4.687541847013479</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.4868977665901184</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.2740314606762853</v>
+        <v>0.3</v>
       </c>
       <c r="JC104" t="n">
-        <v>4.96113048463919</v>
+        <v>4.687542021309787</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.3794798254966736</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.4386651685504979</v>
+        <v>0.3</v>
       </c>
       <c r="JC105" t="n">
-        <v>4.961130628623098</v>
+        <v>4.687542165293696</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.4696042239665985</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.4386651685504979</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC106" t="n">
-        <v>4.961130461904889</v>
+        <v>4.687541998575486</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.3357944190502167</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>4.961130454326788</v>
+        <v>4.687541990997386</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.375007152557373</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>4.961130166358974</v>
+        <v>4.687541703029571</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.4764054417610168</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>4.961130181515175</v>
+        <v>4.687541718185773</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.386292427778244</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.07403146067628527</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>4.961130408858186</v>
+        <v>4.687541945528784</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.5174862146377563</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.2740314606762853</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>4.961130393701985</v>
+        <v>4.687541930372583</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.2829383909702301</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.2740314606762853</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>4.961130499795392</v>
+        <v>4.687542036465988</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.3816576898097992</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4386651685504979</v>
+        <v>0.16</v>
       </c>
       <c r="JC113" t="n">
-        <v>4.961130226983777</v>
+        <v>4.687541763654375</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.478439599275589</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.4386651685504979</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>4.961130325499082</v>
+        <v>4.687541862169679</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.4314011931419373</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.16</v>
       </c>
       <c r="JC115" t="n">
-        <v>4.96113047706109</v>
+        <v>4.687542013731687</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.4348104298114777</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>4.961130492217291</v>
+        <v>4.687542028887888</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.45427206158638</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC117" t="n">
-        <v>4.96113046948299</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.4970958530902863</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC118" t="n">
-        <v>4.961130552842094</v>
+        <v>4.687542089512691</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.3842199444770813</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.16</v>
       </c>
       <c r="JC119" t="n">
-        <v>4.961130651357399</v>
+        <v>4.687542188027996</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.350614994764328</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>4.96113048463919</v>
+        <v>4.687542021309787</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.4093821942806244</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>4.96113046948299</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.4053796827793121</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>4.961130439170588</v>
+        <v>4.687541975841185</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.4471593201160431</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>4.961130424014388</v>
+        <v>4.687541960684985</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.409512847661972</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>4.961130461904889</v>
+        <v>4.687541998575486</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.441785454750061</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.6500000000000004</v>
       </c>
       <c r="JC125" t="n">
-        <v>4.96113047706109</v>
+        <v>4.687542013731687</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4747740626335144</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6386651685504979</v>
+        <v>1</v>
       </c>
       <c r="JC126" t="n">
-        <v>4.96113046948299</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_1_000007.xlsx
+++ b/out/MLP-Mamba1_repeat_1_000007.xlsx
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.4204380214214325</v>
+        <v>0.4204379916191101</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.6155952215194702</v>
+        <v>0.615595281124115</v>
       </c>
       <c r="JB43" t="n">
         <v>0.7199999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.4933322072029114</v>
+        <v>0.4933321475982666</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.16</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.5013241171836853</v>
+        <v>0.5013240575790405</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.5799999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.450870007276535</v>
+        <v>0.4508699774742126</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.7199999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.466746598482132</v>
+        <v>0.4667465388774872</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.4399999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.3449349999427795</v>
+        <v>0.3449349701404572</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.1199999999999999</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.405793696641922</v>
+        <v>0.4057936668395996</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.412027895450592</v>
+        <v>0.4120278656482697</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.4566904902458191</v>
+        <v>0.4566904604434967</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -70904,7 +70904,7 @@
         <v>0.4702053368091583</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
         <v>4.687542112246993</v>
@@ -71699,7 +71699,7 @@
         <v>0.5715712904930115</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
         <v>4.687542119825094</v>
@@ -72494,7 +72494,7 @@
         <v>0.4783316850662231</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
         <v>4.687542385058607</v>
@@ -73289,7 +73289,7 @@
         <v>0.5300479531288147</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
         <v>4.687542089512691</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.5713008046150208</v>
+        <v>0.571300745010376</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
         <v>4.687542332011904</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.4161878526210785</v>
+        <v>0.4161877930164337</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC95" t="n">
         <v>4.687542438105309</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.4216575026512146</v>
+        <v>0.4216575622558594</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.9999999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.478439599275589</v>
+        <v>0.4784396588802338</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.1199999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.4471593201160431</v>
+        <v>0.4471593797206879</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.5799999999999998</v>
